--- a/output/StructureDefinition-pdex-provenance.xlsx
+++ b/output/StructureDefinition-pdex-provenance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2256" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2256" uniqueCount="385">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.1</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-17T14:48:28-05:00</t>
+    <t>2026-03-17T22:49:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -871,10 +871,7 @@
     <t>For example: author, performer, enterer, attester, etc.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-provenance-participant-type</t>
+    <t>http://hl7.org/fhir/us/davinci-pdex/ValueSet/ProvenanceAgentType</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -986,7 +983,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/davinci-pdex/ValueSet/ProvenanceAgentType</t>
+    <t>required</t>
   </si>
   <si>
     <t>Provenance.agent:ProvenanceAuthor.role</t>
@@ -4827,11 +4824,11 @@
         <v>84</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>273</v>
+        <v>182</v>
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
@@ -4864,27 +4861,27 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>278</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4910,13 +4907,13 @@
         <v>232</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4942,14 +4939,14 @@
         <v>84</v>
       </c>
       <c r="X29" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="Y29" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="Y29" t="s" s="2">
+      <c r="Z29" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="Z29" t="s" s="2">
-        <v>285</v>
-      </c>
       <c r="AA29" t="s" s="2">
         <v>84</v>
       </c>
@@ -4966,7 +4963,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -4984,24 +4981,24 @@
         <v>84</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5024,16 +5021,16 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5083,7 +5080,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>94</v>
@@ -5098,16 +5095,16 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>84</v>
@@ -5115,10 +5112,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5141,16 +5138,16 @@
         <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5200,7 +5197,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5218,7 +5215,7 @@
         <v>84</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>84</v>
@@ -5232,13 +5229,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>249</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>84</v>
@@ -5353,7 +5350,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>262</v>
@@ -5468,7 +5465,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>263</v>
@@ -5585,7 +5582,7 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>264</v>
@@ -5704,7 +5701,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>269</v>
@@ -5750,26 +5747,26 @@
         <v>84</v>
       </c>
       <c r="S36" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X36" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>309</v>
+        <v>273</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -5802,27 +5799,27 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>278</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5848,13 +5845,13 @@
         <v>232</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5880,14 +5877,14 @@
         <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="Y37" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="Y37" t="s" s="2">
+      <c r="Z37" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>285</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
       </c>
@@ -5904,7 +5901,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -5922,24 +5919,24 @@
         <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5962,16 +5959,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M38" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6021,7 +6018,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>94</v>
@@ -6036,16 +6033,16 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>84</v>
@@ -6053,10 +6050,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6079,16 +6076,16 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6138,7 +6135,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6156,7 +6153,7 @@
         <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>84</v>
@@ -6170,13 +6167,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>249</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>84</v>
@@ -6204,7 +6201,7 @@
         <v>251</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>253</v>
@@ -6291,7 +6288,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>262</v>
@@ -6406,7 +6403,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>263</v>
@@ -6523,7 +6520,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>264</v>
@@ -6642,7 +6639,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>269</v>
@@ -6688,7 +6685,7 @@
         <v>84</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>84</v>
@@ -6706,10 +6703,10 @@
         <v>182</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
@@ -6742,27 +6739,27 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>278</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6788,13 +6785,13 @@
         <v>232</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6820,14 +6817,14 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="Y45" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="Y45" t="s" s="2">
+      <c r="Z45" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>285</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
       </c>
@@ -6844,7 +6841,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -6862,24 +6859,24 @@
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6902,16 +6899,16 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M46" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6961,7 +6958,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>94</v>
@@ -6976,16 +6973,16 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -6993,10 +6990,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7019,16 +7016,16 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7078,7 +7075,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7096,7 +7093,7 @@
         <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>84</v>
@@ -7110,10 +7107,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7139,10 +7136,10 @@
         <v>250</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7193,7 +7190,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7211,24 +7208,24 @@
         <v>84</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7340,10 +7337,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7369,10 +7366,10 @@
         <v>140</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7453,13 +7450,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>84</v>
@@ -7481,13 +7478,13 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7547,7 +7544,7 @@
         <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>145</v>
@@ -7570,10 +7567,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7685,10 +7682,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7714,10 +7711,10 @@
         <v>140</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7800,10 +7797,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7829,13 +7826,13 @@
         <v>108</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7843,49 +7840,49 @@
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>94</v>
@@ -7917,10 +7914,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7946,10 +7943,10 @@
         <v>232</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7976,29 +7973,29 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8030,10 +8027,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8149,10 +8146,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8178,10 +8175,10 @@
         <v>114</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8208,14 +8205,14 @@
         <v>84</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="Y57" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="Z57" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>366</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
       </c>
@@ -8232,7 +8229,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>94</v>
@@ -8250,24 +8247,24 @@
         <v>84</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8293,13 +8290,13 @@
         <v>152</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8349,7 +8346,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>94</v>
@@ -8367,10 +8364,10 @@
         <v>84</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>84</v>
@@ -8381,10 +8378,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8410,13 +8407,13 @@
         <v>85</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8466,7 +8463,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -8484,7 +8481,7 @@
         <v>84</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>84</v>
@@ -8498,10 +8495,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8524,13 +8521,13 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8581,7 +8578,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -8599,7 +8596,7 @@
         <v>84</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>84</v>

--- a/output/StructureDefinition-pdex-provenance.xlsx
+++ b/output/StructureDefinition-pdex-provenance.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T22:49:33-04:00</t>
+    <t>2026-03-19T09:51:30-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-pdex-provenance.xlsx
+++ b/output/StructureDefinition-pdex-provenance.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T09:51:30-04:00</t>
+    <t>2026-03-31T21:00:10-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-pdex-provenance.xlsx
+++ b/output/StructureDefinition-pdex-provenance.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T21:00:10-04:00</t>
+    <t>2026-05-29T12:37:47-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
